--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -20,7 +20,7 @@
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin2018-08-13 00:00:00</t>
+    <t>Origin2018-08-15 00:00:00</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -65,7 +65,7 @@
     <t>Multan</t>
   </si>
   <si>
-    <t>DSR2018-08-13 00:00:00</t>
+    <t>DSR2018-08-15 00:00:00</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
@@ -529,27 +529,12 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>110</v>
-      </c>
-      <c r="F6" s="1">
-        <v>4222</v>
-      </c>
-      <c r="G6" s="1">
-        <v>55</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2111</v>
-      </c>
-      <c r="I6">
-        <v>2.6054002842255</v>
-      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1">
@@ -707,27 +692,6 @@
       </c>
       <c r="B20" t="s">
         <v>19</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>110</v>
-      </c>
-      <c r="F20">
-        <v>4222</v>
-      </c>
-      <c r="G20">
-        <v>55</v>
-      </c>
-      <c r="H20">
-        <v>2111</v>
-      </c>
-      <c r="I20">
-        <v>2.6054002842255</v>
       </c>
     </row>
     <row r="21" spans="1:9">

--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
   <si>
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin2018-08-15 00:00:00</t>
+    <t>Origin 2018-08-31</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -65,7 +65,7 @@
     <t>Multan</t>
   </si>
   <si>
-    <t>DSR2018-08-15 00:00:00</t>
+    <t>DSR 2018-08-31</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Mohr-Collier</t>
+  </si>
+  <si>
+    <t>Torp, Stamm and Wilkinson</t>
   </si>
 </sst>
 </file>
@@ -434,8 +437,8 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="30" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
@@ -462,260 +465,149 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="1" t="s">
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
         <v>6</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
   <si>
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin 2018-08-31</t>
+    <t>Origin 2018-08-13</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -65,7 +65,13 @@
     <t>Multan</t>
   </si>
   <si>
-    <t>DSR 2018-08-31</t>
+    <t>Another faltu city</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>DSR 2018-08-13</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
@@ -84,9 +90,6 @@
   </si>
   <si>
     <t>Mohr-Collier</t>
-  </si>
-  <si>
-    <t>Torp, Stamm and Wilkinson</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -508,6 +511,27 @@
       <c r="B6" t="s">
         <v>13</v>
       </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>110</v>
+      </c>
+      <c r="F6">
+        <v>4222</v>
+      </c>
+      <c r="G6">
+        <v>55</v>
+      </c>
+      <c r="H6">
+        <v>2111</v>
+      </c>
+      <c r="I6">
+        <v>2.6054002842255</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
@@ -525,12 +549,28 @@
         <v>15</v>
       </c>
     </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
@@ -559,7 +599,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -567,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -575,7 +615,28 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>110</v>
+      </c>
+      <c r="F24">
+        <v>4222</v>
+      </c>
+      <c r="G24">
+        <v>55</v>
+      </c>
+      <c r="H24">
+        <v>2111</v>
+      </c>
+      <c r="I24">
+        <v>2.6054002842255</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -583,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -591,7 +652,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -599,15 +660,7 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28">
-        <v>7</v>
-      </c>
-      <c r="B28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
   <si>
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin 2018-08-13</t>
+    <t>Origin 2018-09-12</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -44,52 +44,22 @@
     <t>% Rev. on Cash Collection</t>
   </si>
   <si>
-    <t>Multiple</t>
-  </si>
-  <si>
-    <t>Abbottabad</t>
-  </si>
-  <si>
-    <t>Bahawalpur</t>
-  </si>
-  <si>
-    <t>Islamabad</t>
-  </si>
-  <si>
     <t>Karachi</t>
   </si>
   <si>
-    <t>Lahore</t>
-  </si>
-  <si>
-    <t>Multan</t>
-  </si>
-  <si>
-    <t>Another faltu city</t>
-  </si>
-  <si>
-    <t>Hyderabad</t>
-  </si>
-  <si>
-    <t>DSR 2018-08-13</t>
+    <t>DSR 2018-09-12</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
   </si>
   <si>
-    <t>Murphy PLC</t>
-  </si>
-  <si>
-    <t>Swift LLC</t>
-  </si>
-  <si>
     <t>Stehr LLC</t>
   </si>
   <si>
     <t>Bruen Inc</t>
   </si>
   <si>
-    <t>Mohr-Collier</t>
+    <t>Bibi</t>
   </si>
 </sst>
 </file>
@@ -440,7 +410,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -480,97 +450,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>110</v>
-      </c>
-      <c r="F6">
-        <v>4222</v>
-      </c>
-      <c r="G6">
-        <v>55</v>
-      </c>
-      <c r="H6">
-        <v>2111</v>
-      </c>
-      <c r="I6">
-        <v>2.6054002842255</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
@@ -599,7 +484,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -607,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -615,28 +500,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>110</v>
-      </c>
-      <c r="F24">
-        <v>4222</v>
-      </c>
-      <c r="G24">
-        <v>55</v>
-      </c>
-      <c r="H24">
-        <v>2111</v>
-      </c>
-      <c r="I24">
-        <v>2.6054002842255</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -644,23 +508,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27">
-        <v>6</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
   <si>
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin 2018-09-12</t>
+    <t>Origin 2018-08-13</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -44,10 +44,34 @@
     <t>% Rev. on Cash Collection</t>
   </si>
   <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>Abbottabad</t>
+  </si>
+  <si>
+    <t>Bahawalpur</t>
+  </si>
+  <si>
+    <t>Islamabad</t>
+  </si>
+  <si>
     <t>Karachi</t>
   </si>
   <si>
-    <t>DSR 2018-09-12</t>
+    <t>Lahore</t>
+  </si>
+  <si>
+    <t>Multan</t>
+  </si>
+  <si>
+    <t>Another faltu city</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>DSR 2018-08-13</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
@@ -450,12 +474,97 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>110</v>
+      </c>
+      <c r="F6">
+        <v>4222</v>
+      </c>
+      <c r="G6">
+        <v>55</v>
+      </c>
+      <c r="H6">
+        <v>2111</v>
+      </c>
+      <c r="I6">
+        <v>2.6054002842255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
@@ -484,7 +593,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -492,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -500,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -508,7 +617,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
   <si>
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin 2018-08-13</t>
+    <t>Origin 2018-09-22</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -71,16 +71,22 @@
     <t>Hyderabad</t>
   </si>
   <si>
-    <t>DSR 2018-08-13</t>
+    <t>DSR 2018-09-22</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
   </si>
   <si>
+    <t>Murphy PLC</t>
+  </si>
+  <si>
     <t>Stehr LLC</t>
   </si>
   <si>
     <t>Bruen Inc</t>
+  </si>
+  <si>
+    <t>Mohr-Collier</t>
   </si>
   <si>
     <t>Bibi</t>
@@ -434,7 +440,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -505,27 +511,6 @@
       <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>110</v>
-      </c>
-      <c r="F6">
-        <v>4222</v>
-      </c>
-      <c r="G6">
-        <v>55</v>
-      </c>
-      <c r="H6">
-        <v>2111</v>
-      </c>
-      <c r="I6">
-        <v>2.6054002842255</v>
-      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
@@ -618,6 +603,22 @@
       </c>
       <c r="B25" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -20,7 +20,7 @@
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin 2018-09-22</t>
+    <t>Origin 2018-09-24</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -71,7 +71,7 @@
     <t>Hyderabad</t>
   </si>
   <si>
-    <t>DSR 2018-09-22</t>
+    <t>DSR 2018-09-24</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
@@ -440,7 +440,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -511,6 +511,21 @@
       <c r="B6" t="s">
         <v>13</v>
       </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>75</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
@@ -544,82 +559,108 @@
         <v>17</v>
       </c>
     </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>75</v>
+      </c>
+      <c r="H14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27">
-        <v>6</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/public/reports/daily_pickup_sales_report.xlsx
+++ b/public/reports/daily_pickup_sales_report.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
   <si>
     <t>S. No.</t>
   </si>
   <si>
-    <t>Origin 2018-09-24</t>
+    <t>Origin 2018-09-27</t>
   </si>
   <si>
     <t>No. of Parcels Booked</t>
@@ -32,46 +32,25 @@
     <t>Revenue without GST</t>
   </si>
   <si>
-    <t>COD Collection</t>
+    <t>Collection Amount</t>
   </si>
   <si>
     <t>Avg/Parcel Revenue</t>
   </si>
   <si>
-    <t>Avg. Cash Collection</t>
-  </si>
-  <si>
-    <t>% Rev. on Cash Collection</t>
-  </si>
-  <si>
-    <t>Multiple</t>
-  </si>
-  <si>
-    <t>Abbottabad</t>
-  </si>
-  <si>
-    <t>Bahawalpur</t>
-  </si>
-  <si>
-    <t>Islamabad</t>
+    <t>Avg. Amount Collection</t>
+  </si>
+  <si>
+    <t>% Rev. on Amount Collection</t>
   </si>
   <si>
     <t>Karachi</t>
   </si>
   <si>
-    <t>Lahore</t>
-  </si>
-  <si>
-    <t>Multan</t>
-  </si>
-  <si>
-    <t>Another faltu city</t>
-  </si>
-  <si>
-    <t>Hyderabad</t>
-  </si>
-  <si>
-    <t>DSR 2018-09-24</t>
+    <t>Matyari</t>
+  </si>
+  <si>
+    <t>DSR 2018-09-27</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
@@ -97,18 +76,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
       <u val="none"/>
@@ -134,12 +104,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,35 +407,35 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -479,6 +446,27 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>450</v>
+      </c>
+      <c r="F2">
+        <v>14100</v>
+      </c>
+      <c r="G2">
+        <v>225</v>
+      </c>
+      <c r="H2">
+        <v>7050</v>
+      </c>
+      <c r="I2">
+        <v>3.1914893617021</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
@@ -488,179 +476,103 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
+      <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>75</v>
-      </c>
-      <c r="H6">
-        <v>75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C11">
         <v>18</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D11">
         <v>2</v>
       </c>
-      <c r="D12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H12" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>75</v>
-      </c>
-      <c r="H14">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="E11">
+        <v>450</v>
+      </c>
+      <c r="F11">
+        <v>14100</v>
+      </c>
+      <c r="G11">
+        <v>225</v>
+      </c>
+      <c r="H11">
+        <v>7050</v>
+      </c>
+      <c r="I11">
+        <v>3.1914893617021</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
